--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-19.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-19.xlsx
@@ -474,751 +474,751 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583988739476</v>
+        <v>5583998533337</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>Edinaldo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Michel Bruno Santos Gonçalves</t>
+          <t>Edinaldo Santos de Andrade</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583996425335</v>
+        <v>5583986292098</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fabricio</t>
+          <t>Claudenice</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fabricio Silva de Oliveira</t>
+          <t>Claudenice Pereira Mendes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583996023349</v>
+        <v>5583998464502</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Gean</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Maria Gilcelia Pereira de Oliveira</t>
+          <t>Gean Carlos de Sousa Queiroz Freire</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583991759845</v>
+        <v>5583981687726</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wellinton</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wellinton da Silva Brito</t>
+          <t>Maria Vitória</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583998565577</v>
+        <v>5583999886965</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Carla</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Carla Janne de Sousa Oliveira</t>
+          <t>Ana Clara Mendes Leite</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583988121501</v>
+        <v>5583991679589</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Matheus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fabio Henrique Farias de Oliveira</t>
+          <t>Matheus Andrade Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583988897250</v>
+        <v>5511954995387</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wanderson</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wanderson Dantas de Morais</t>
+          <t>Jose Ivanildo Martins Fernandes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583988634691</v>
+        <v>5583986122161</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Maria Jose Henrique</t>
+          <t>Jose Lins Bezerra</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583991286535</v>
+        <v>5583996193565</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>Semas</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Paulo de Tarso Campos de Carvalho</t>
+          <t>Semas</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583988207701</v>
+        <v>5583988741407</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Katia</t>
+          <t>Ariana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Katia Vale</t>
+          <t>Ariana Batista Leite</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583999031848</v>
+        <v>5583998573498</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Aaoml</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lucas Ravi</t>
+          <t>Aaoml</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583993345558</v>
+        <v>5583996816746</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Geoliana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jose Ronaldo dos Santos Silva</t>
+          <t>Geoliana Nobrega</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583987721999</v>
+        <v>5583999466313</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>61.316.248</t>
+          <t>Jorge</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>61.316.248 Joseane Silva de Souza</t>
+          <t>Jorge Ramos da Silva</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583996454142</v>
+        <v>5583999134287</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ana Maria Belarmino dos Santos</t>
+          <t>Lucas da Silva Alves</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583998534307</v>
+        <v>5583988739476</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Luiz</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luiz do Carmo Filho</t>
+          <t>Michel Bruno Santos Gonçalves</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583987161343</v>
+        <v>5583996425335</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cileide</t>
+          <t>Fabricio</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cileide Maria da Silva Gomes</t>
+          <t>Fabricio Silva de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5581997912270</v>
+        <v>5583996023349</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tatiana</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tatiana Anita de Araujo Pereira Bonifacio</t>
+          <t>Maria Gilcelia Pereira de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583988890119</v>
+        <v>5583991759845</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Iracilda</t>
+          <t>Wellinton</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iracilda Marinho de Carvalho Silva</t>
+          <t>Wellinton da Silva Brito</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583981822063</v>
+        <v>5583998565577</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Senac-ar/pb</t>
+          <t>Carla</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Senac-Ar/Pb</t>
+          <t>Carla Janne de Sousa Oliveira</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583988419160</v>
+        <v>5583988121501</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nippon</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nippon</t>
+          <t>Fabio Henrique Farias de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583991345162</v>
+        <v>5583988897250</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Wanderson</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fabio de Lima Martins</t>
+          <t>Wanderson Dantas de Morais</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583993601917</v>
+        <v>5583988634691</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nilton</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nilton Luiz Gomes de Lima</t>
+          <t>Maria Jose Henrique</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5583991491413</v>
+        <v>5583991286535</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Angelo</t>
+          <t>Paulo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Angelo Estevao Machado</t>
+          <t>Paulo de Tarso Campos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583993810303</v>
+        <v>5583988207701</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Katia</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Casa dos Sonhos -Cds</t>
+          <t>Katia Vale</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5511981115200</v>
+        <v>5583999031848</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central Geral do Dizimo - Pro-Vida</t>
+          <t>Lucas Ravi</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583981579515</v>
+        <v>5583993345558</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Maria do Livramento Medeiros</t>
+          <t>Jose Ronaldo dos Santos Silva</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583996828797</v>
+        <v>5583987721999</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Alessandra</t>
+          <t>61.316.248</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alessandra da Silva</t>
+          <t>61.316.248 Joseane Silva de Souza</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583996610166</v>
+        <v>5583996454142</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rodolfo</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rodolfo de Araujo Pereira</t>
+          <t>Ana Maria Belarmino dos Santos</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583987884538</v>
+        <v>5583998534307</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Abmael</t>
+          <t>Luiz</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Abmael da Silva Ferreira</t>
+          <t>Luiz do Carmo Filho</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5583999740958</v>
+        <v>5583987161343</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Augusto</t>
+          <t>Cileide</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Augusto Quirino Nunes Neto</t>
+          <t>Cileide Maria da Silva Gomes</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583987863738</v>
+        <v>5581997912270</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Maristela</t>
+          <t>Tatiana</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Maristela Benicio Goncalves Rodrigues</t>
+          <t>Tatiana Anita de Araujo Pereira Bonifacio</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5583987287200</v>
+        <v>5583988890119</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Iracilda</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jose Ricardo Pereira Alves</t>
+          <t>Iracilda Marinho de Carvalho Silva</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583988089457</v>
+        <v>5583981822063</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>Senac-ar/pb</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pedro Lucas dos Santos Almeida</t>
+          <t>Senac-Ar/Pb</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583996044729</v>
+        <v>5583988419160</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mauricelia</t>
+          <t>Nippon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mauricelia Teodosio</t>
+          <t>Nippon</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583986672841</v>
+        <v>5583991345162</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gregorio</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gregorio Chavier Marinheiro da Costa</t>
+          <t>Fabio de Lima Martins</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5583991885432</v>
+        <v>5583993601917</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vania</t>
+          <t>Nilton</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Vania do Nascimento Pereira</t>
+          <t>Nilton Luiz Gomes de Lima</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583986353681</v>
+        <v>5583991491413</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Girlane</t>
+          <t>Angelo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Girlane Tomaz</t>
+          <t>Angelo Estevao Machado</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5568984224915</v>
+        <v>5583993810303</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Manoel</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Manoel de Nazare Ribeiro da Cruz Junior</t>
+          <t>Casa dos Sonhos -Cds</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5583988118074</v>
+        <v>5511981115200</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Idetonio</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Idetonio de Franca</t>
+          <t>Central Geral do Dizimo - Pro-Vida</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5583996637543</v>
+        <v>5583981579515</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jose Victor Felix Moura</t>
+          <t>Maria do Livramento Medeiros</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583999122456</v>
+        <v>5583996828797</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wallace</t>
+          <t>Alessandra</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wallace Patrick Santos de Farias Souza</t>
+          <t>Alessandra da Silva</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583986397335</v>
+        <v>5583996610166</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Danielly</t>
+          <t>Rodolfo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Danielly de Souza Cruz</t>
+          <t>Rodolfo de Araujo Pereira</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583996332588</v>
+        <v>5583987884538</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Abmael</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jessica Rodrigues de Oliveira</t>
+          <t>Abmael da Silva Ferreira</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583987016043</v>
+        <v>5583999740958</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Chislania</t>
+          <t>Augusto</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chislania de Lima Felix</t>
+          <t>Augusto Quirino Nunes Neto</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583996000868</v>
+        <v>5583987863738</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Maristela</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fernando Brito da Silva</t>
+          <t>Maristela Benicio Goncalves Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583988906883</v>
+        <v>5583987287200</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Climario</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Climario</t>
+          <t>Jose Ricardo Pereira Alves</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583982105773</v>
+        <v>5583988089457</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hugo</t>
+          <t>Pedro</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hugo Fernandes de Castro</t>
+          <t>Pedro Lucas dos Santos Almeida</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583989150934</v>
+        <v>5583999666372</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>Egon</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Francisco da Mata</t>
+          <t>Egon Marcelo de Oliveira Fernandes</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583996546247</v>
+        <v>5583996044729</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Joelio</t>
+          <t>Mauricelia</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Joelio Santos de Oliveira</t>
+          <t>Mauricelia Teodosio</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583988341679</v>
+        <v>5583986672841</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>Gregorio</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Francisco Ramalho Sales</t>
+          <t>Gregorio Chavier Marinheiro da Costa</t>
         </is>
       </c>
     </row>
